--- a/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>26784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>29485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>41376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>65364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>75380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101135</t>
+          <t>100456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89272</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117514</t>
+          <t>118167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>173506</t>
+          <t>170726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212216</t>
+          <t>209414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209182</t>
+          <t>209861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>235199</t>
+          <t>234937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236122</t>
+          <t>235469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264364</t>
+          <t>263144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>451737</t>
+          <t>454539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>490447</t>
+          <t>493227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80838</t>
+          <t>81261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105883</t>
+          <t>106588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77705</t>
+          <t>77094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95464</t>
+          <t>95238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71290</t>
+          <t>72178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>88568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154240</t>
+          <t>153535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179285</t>
+          <t>178862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>143346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176257</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343019</t>
+          <t>343331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327102</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361849</t>
+          <t>360013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351638</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688889</t>
+          <t>688577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>736872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>47066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56647</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>84807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99083</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>243497</t>
+          <t>242738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264626</t>
+          <t>264712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273002</t>
+          <t>273686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294321</t>
+          <t>294881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>523154</t>
+          <t>522318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>553605</t>
+          <t>554690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44842</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66161</t>
+          <t>65477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90211</t>
+          <t>89126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120662</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92689</t>
+          <t>92681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105028</t>
+          <t>105163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103708</t>
+          <t>104396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119104</t>
+          <t>120132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201722</t>
+          <t>201665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221585</t>
+          <t>221682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52003</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>380002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>407294</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>433225</t>
+          <t>436171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>461879</t>
+          <t>462974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>824703</t>
+          <t>822566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>862665</t>
+          <t>861399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>75177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104926</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152450</t>
+          <t>153716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190412</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>42914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>59152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74362</t>
+          <t>73263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217397</t>
+          <t>218411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245778</t>
+          <t>245064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>234856</t>
+          <t>234788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>264379</t>
+          <t>265483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460632</t>
+          <t>459912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>501198</t>
+          <t>501759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96349</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124730</t>
+          <t>123716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110334</t>
+          <t>109230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139857</t>
+          <t>139925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215641</t>
+          <t>215080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256207</t>
+          <t>256927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>81719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99750</t>
+          <t>98484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95335</t>
+          <t>94516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112140</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181513</t>
+          <t>181243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205638</t>
+          <t>205790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>34774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>51539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41863</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64817</t>
+          <t>64665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88942</t>
+          <t>89212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>334612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>368716</t>
+          <t>370677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>372009</t>
+          <t>373103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>409489</t>
+          <t>409824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717982</t>
+          <t>718387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>767086</t>
+          <t>767403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183121</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>151907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189722</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359774</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>35796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58784</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>40924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57898</t>
+          <t>57482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81161</t>
+          <t>80886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116739</t>
+          <t>119500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166779</t>
+          <t>167040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168891</t>
+          <t>169526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219775</t>
+          <t>217673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303087</t>
+          <t>300778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372091</t>
+          <t>368967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291724</t>
+          <t>291463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341764</t>
+          <t>339003</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295423</t>
+          <t>297525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346307</t>
+          <t>345672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601610</t>
+          <t>604734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670614</t>
+          <t>672923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57319</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69313</t>
+          <t>69089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97774</t>
+          <t>96244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102428</t>
+          <t>102690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120687</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124794</t>
+          <t>125323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146719</t>
+          <t>146765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233300</t>
+          <t>234830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>261985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176087</t>
+          <t>178285</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228995</t>
+          <t>230011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>234238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>289888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>428119</t>
+          <t>427021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505938</t>
+          <t>505411</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>433147</t>
+          <t>432131</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>486055</t>
+          <t>483857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>468036</t>
+          <t>469427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>522644</t>
+          <t>525077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915519</t>
+          <t>916046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993338</t>
+          <t>994436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13377</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8564</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18331</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>20742</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15086</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26977</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15540</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26674</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13377</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9103</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18901</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>42365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33040</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42807</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>73,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35720</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29485</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41376</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29788</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>40922</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37994</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>32470</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42268</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>73,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65364</t>
+          <t>65468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81049</t>
+          <t>80955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103824</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90272</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>117629</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>88297</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>75380</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>100456</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>76769</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>102055</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>103824</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>90492</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>118167</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170726</t>
+          <t>174107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209414</t>
+          <t>212398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>249812</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>236007</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>263364</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>222020</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>209861</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>234937</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>208262</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>233548</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>249812</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>235469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>263144</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454539</t>
+          <t>451555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493227</t>
+          <t>489846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42837</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34997</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52388</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>50057</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41343</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59487</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>41106</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>59676</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>36,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42837</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34974</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51364</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106588</t>
+          <t>104740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80705</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71154</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88545</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>86524</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77094</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>95238</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76905</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95475</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>63,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80705</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72178</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88568</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153535</t>
+          <t>155383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178862</t>
+          <t>179311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>142875</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>177263</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>143346</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>175521</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>141828</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>176193</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>145465</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>180130</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295036</t>
+          <t>293215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343331</t>
+          <t>342599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>368511</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>351286</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>385674</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>344263</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>327838</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>360013</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>327166</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>361531</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>368511</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>348419</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>383084</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688577</t>
+          <t>689309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736872</t>
+          <t>738693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47016</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56599</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39578</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44209</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33783</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44602</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47066</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56448</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84807</t>
+          <t>83804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>99605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9383</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15074</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15906</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11275</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22164</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10882</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21701</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9383</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5642</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15024</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>284546</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>273951</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>294350</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>254744</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>242738</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>264712</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>243090</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>264162</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>83,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>284546</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>273686</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>294881</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>83,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>522318</t>
+          <t>523339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>554690</t>
+          <t>554142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54617</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44813</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>65212</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49909</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39941</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61915</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40491</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>61563</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54617</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>44282</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89126</t>
+          <t>89674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121498</t>
+          <t>120477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,74 +3012,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>112547</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103879</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>118862</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99483</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92681</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105163</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>91852</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105169</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>85,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>112547</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104396</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>120132</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>299</t>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201665</t>
+          <t>201342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221682</t>
+          <t>220733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24351</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18036</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33019</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17344</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11664</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24146</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11658</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24975</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>14,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24351</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>16766</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32502</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>52383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>436342</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>464031</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>569</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>380002</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>407906</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>379722</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>407139</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>436171</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>462974</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>822566</t>
+          <t>824311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>861399</t>
+          <t>862397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88350</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74120</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>101809</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>83159</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69059</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>69826</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>97243</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>17,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>88350</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75177</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>101980</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>152718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>190804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38483</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33001</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43030</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28338</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23220</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32781</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23419</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33059</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38483</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32907</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42914</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59152</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73263</t>
+          <t>73678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6790</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16819</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>12303</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7860</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17421</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17222</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6906</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16913</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49820</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49820</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49820</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49820</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49820</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>249436</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>233461</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>265073</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>355</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>232004</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>218411</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>245064</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>217644</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>246338</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>249436</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>234788</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>265483</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>66,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459912</t>
+          <t>462327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>501945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125277</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109640</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>141252</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>110123</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123716</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95789</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>124483</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>125277</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>109230</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>139925</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215080</t>
+          <t>214894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256927</t>
+          <t>254512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>374713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>374713</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>374713</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>515</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>342127</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>342127</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>342127</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>374713</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>374713</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>374713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103753</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95238</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>111643</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>69,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>90604</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81719</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98484</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>80851</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98374</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>103753</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>94516</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>110659</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>75,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181243</t>
+          <t>180568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205790</t>
+          <t>205760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33445</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25555</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41960</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>42654</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34774</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51539</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34884</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52407</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33445</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26539</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>42682</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64665</t>
+          <t>64695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89212</t>
+          <t>89887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>137198</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>137198</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>137198</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>133258</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>133258</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>133258</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>137198</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>137198</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>137198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>372627</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>408700</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>334612</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>370677</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>333199</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>367020</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>373103</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>409824</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>718387</t>
+          <t>719347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>767403</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -5076,67 +5076,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>170058</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153031</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>189104</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>165080</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>145348</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>181413</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>149005</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>182826</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>170058</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>151907</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>188628</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310353</t>
+          <t>311700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359369</t>
+          <t>358409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>776</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>516025</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23275</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16759</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29496</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21206</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13754</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31989</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>40590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35796</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>50343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33457</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27236</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39973</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>58,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33472</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22689</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40924</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>61,22%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>23501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57482</t>
+          <t>53147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80886</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>180110</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>161010</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>206673</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>147169</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>119500</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>167040</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>190467</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169526</t>
+          <t>133645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217673</t>
+          <t>168392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>337636</t>
+          <t>328905</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>302614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>368967</t>
+          <t>357423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>294310</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>267747</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>313410</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>311334</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>291463</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>339003</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>324731</t>
+          <t>282046</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297525</t>
+          <t>262448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345672</t>
+          <t>297195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>636065</t>
+          <t>576355</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604734</t>
+          <t>547837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672923</t>
+          <t>602646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474420</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474420</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474420</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458503</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458503</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458503</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515198</t>
+          <t>430840</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515198</t>
+          <t>430840</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515198</t>
+          <t>430840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>973701</t>
+          <t>905260</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>973701</t>
+          <t>905260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>973701</t>
+          <t>905260</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43869</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34178</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54659</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36309</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27869</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46272</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56790</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>82194</t>
+          <t>79655</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69089</t>
+          <t>67002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96244</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123402</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>112612</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133093</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>112653</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102690</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>121093</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136227</t>
+          <t>113598</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>103806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146765</t>
+          <t>120468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>248880</t>
+          <t>237000</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234830</t>
+          <t>223970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261985</t>
+          <t>249653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167271</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167271</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167271</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148962</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148962</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148962</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182113</t>
+          <t>149384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182113</t>
+          <t>149384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182113</t>
+          <t>149384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331074</t>
+          <t>316655</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331074</t>
+          <t>316655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331074</t>
+          <t>316655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>223101</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>272696</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>178285</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>230011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234238</t>
+          <t>181994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289888</t>
+          <t>221161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>427021</t>
+          <t>418762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505411</t>
+          <t>483949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>451169</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>425727</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>475322</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>457458</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>432131</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>483857</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>498180</t>
+          <t>425087</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>469427</t>
+          <t>405821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525077</t>
+          <t>444988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>955638</t>
+          <t>876255</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>916046</t>
+          <t>841455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>994436</t>
+          <t>906642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662142</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662142</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662142</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>626982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>626982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>626982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1421457</t>
+          <t>1325404</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1421457</t>
+          <t>1325404</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1421457</t>
+          <t>1325404</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
